--- a/Project_ETF/ETF_Investment_Portfolio/00878/ETF_Investment_Portfolio_20260610.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00878/ETF_Investment_Portfolio_20260610.xlsx
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>10.51%</t>
+          <t>10.92%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>10.17%</t>
+          <t>10.27%</t>
         </is>
       </c>
     </row>
@@ -655,12 +655,12 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>377,008,486</t>
+          <t>376,289,486</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>6.51%</t>
+          <t>6.39%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>5.23%</t>
+          <t>5.02%</t>
         </is>
       </c>
     </row>
@@ -699,12 +699,12 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>108,074,000</t>
+          <t>109,574,000</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>3.98%</t>
+          <t>4.15%</t>
         </is>
       </c>
     </row>
@@ -721,12 +721,12 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>185,521,000</t>
+          <t>185,167,000</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>3.93%</t>
+          <t>3.73%</t>
         </is>
       </c>
     </row>
@@ -743,12 +743,12 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>2,531</t>
+          <t>2,401</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.75%</t>
+          <t>3.54%</t>
         </is>
       </c>
     </row>
@@ -765,320 +765,320 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>5,010,000</t>
+          <t>5,000,000</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.72%</t>
+          <t>3.53%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>富邦金</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>134,749,945</t>
+          <t>25,748,000</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>2.80%</t>
+          <t>2.82%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>2887</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>台新新光金</t>
+          <t>富邦金</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>569,427,000</t>
+          <t>134,492,945</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.79%</t>
+          <t>2.80%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>2887</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>台新新光金</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>25,748,000</t>
+          <t>569,427,000</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.78%</t>
+          <t>2.80%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>遠傳</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>29,270,000</t>
+          <t>144,292,000</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.65%</t>
+          <t>2.61%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>遠傳</t>
+          <t>台灣大</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>144,292,000</t>
+          <t>129,747,000</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.53%</t>
+          <t>2.60%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>台灣大</t>
+          <t>兆豐金</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>129,747,000</t>
+          <t>343,589,964</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.52%</t>
+          <t>2.54%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>93,188,442</t>
+          <t>30,366,000</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>2.49%</t>
+          <t>2.47%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>兆豐金</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>343,589,964</t>
+          <t>28,864,000</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>2.48%</t>
+          <t>2.46%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>25,984,000</t>
+          <t>93,188,442</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>2.45%</t>
+          <t>2.42%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>2885</t>
+          <t>1216</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>元大金</t>
+          <t>統一</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>227,566,516</t>
+          <t>191,517,000</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>2.45%</t>
+          <t>2.42%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>2885</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>元大金</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>30,366,000</t>
+          <t>227,132,516</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>2.42%</t>
+          <t>2.41%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>1216</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>統一</t>
+          <t>中華電</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>191,517,000</t>
+          <t>97,767,000</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>2.35%</t>
+          <t>2.39%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>62,675,000</t>
+          <t>25,934,000</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>2.33%</t>
+          <t>2.38%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>中華電</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>97,767,000</t>
+          <t>62,556,000</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>2.30%</t>
+          <t>2.27%</t>
         </is>
       </c>
     </row>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>2.18%</t>
+          <t>2.14%</t>
         </is>
       </c>
     </row>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>2.10%</t>
+          <t>2.01%</t>
         </is>
       </c>
     </row>
@@ -1144,51 +1144,51 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.99%</t>
+          <t>1.96%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>3293</t>
+          <t>2880</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>鈊  象</t>
+          <t>華南金</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>14,243,000</t>
+          <t>324,375,000</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.89%</t>
+          <t>1.95%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>2880</t>
+          <t>3293</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>華南金</t>
+          <t>鈊  象</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>319,175,000</t>
+          <t>14,243,000</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>1.88%</t>
+          <t>1.93%</t>
         </is>
       </c>
     </row>
@@ -1205,56 +1205,56 @@
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>48,547,000</t>
+          <t>48,997,000</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>1.80%</t>
+          <t>1.90%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>5876</t>
+          <t>5871</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>上海商銀</t>
+          <t>中租-KY</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>242,825,590</t>
+          <t>85,399,080</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>1.72%</t>
+          <t>1.74%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>5871</t>
+          <t>5876</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>中租-KY</t>
+          <t>上海商銀</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>85,399,080</t>
+          <t>242,825,590</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>1.69%</t>
+          <t>1.74%</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>1.65%</t>
+          <t>1.71%</t>
         </is>
       </c>
     </row>
@@ -1293,7 +1293,7 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>28,892,324,223</t>
+          <t>13,922,448,474</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr"/>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>10,288,502,127</t>
+          <t>9,625,516,162</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr"/>
@@ -1329,7 +1329,7 @@
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>-4,401,820,861</t>
+          <t>-2,861,506,446</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr"/>
